--- a/data/raw/user_questions/QA_datasets.xlsx
+++ b/data/raw/user_questions/QA_datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT\THI\PAPER\project\neurosymbolic-legal-reasoner\data\raw\user_questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF4E899-359C-4905-9A43-289394AE7F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAE33D5-7F57-4686-B91E-7B2DDCAAE9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1835,7 +1835,7 @@
   <cols>
     <col min="1" max="1" width="24.77734375" style="6" customWidth="1"/>
     <col min="2" max="2" width="21.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="183.77734375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="53.88671875" style="6" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="59" style="6" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="6"/>
@@ -1888,7 +1888,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="228" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="216" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="336" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="324" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="132" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="120" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="84" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>148</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="108" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="96" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>160</v>
       </c>

--- a/data/raw/user_questions/QA_datasets.xlsx
+++ b/data/raw/user_questions/QA_datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT\THI\PAPER\project\neurosymbolic-legal-reasoner\data\raw\user_questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAE33D5-7F57-4686-B91E-7B2DDCAAE9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84026B6E-CB58-408E-8283-1387B011D58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,16 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="184">
-  <si>
-    <t>Câu hỏi</t>
-  </si>
-  <si>
-    <t>Câu trả lời luật sư</t>
-  </si>
-  <si>
-    <t>legal_references Luật sư</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="189">
   <si>
     <t>Nguồn câu hỏi</t>
   </si>
@@ -90,9 +81,6 @@
   </si>
   <si>
     <t>Chủ tịch HĐQT bị tạm giam thì có điều hành công ty được không?</t>
-  </si>
-  <si>
-    <t>Chủ đề câu hỏi</t>
   </si>
   <si>
     <t>Khoản 4, Điều 156 Luật Doanh nghiệp 2020 quy định:
@@ -1432,6 +1420,33 @@
 Cách địa điểm A trên một số nhà nữa, doanh nghiệp có thuê một cái kho tại địa điểm làm chỗ để hàng của công ty thì theo quy định nói trên về địa điểm kinh doanh và hoạt động kinh doanh của doanh nghiệp, kho chứa hàng là một tên gọi khác của một đơn vị phụ thuộc. Xét về chức năng kinh doanh, kho chứa hàng có chức năng lưu giữ hàng hóa của doanh nghiệp và có thể kinh doanh hàng hóa khi cần thiết. Vì thế doanh nghiệp nên đăng ký kho chứa hàng là địa điểm kinh doanh của doanh nghiệp.
 Sau khi tiến hành thủ tục thành lập địa điểm kinh doanh, doanh nghiệp làm thủ tục thông báo và kê khai với cơ quan thuế về việc thành lập thêm địa điểm kinh doanh trực thuộc doanh nghiệp để cơ quan thuế quản lý. Trong trường hợp này kho hàng cùng tỉnh, thành phố nơi doanh nghiệp đặt trụ sở chính thì doanh nghiệp chịu trách nhiệm kê khai và nộp Thuế môn bài, Thuế GTGT cho kho hàng (địa điểm kinh doanh) tại cơ quan thuế quản lý trực tiếp Công ty.
 Nếu doanh nghiệp thuê kho chứa hàng, có hợp đồng, hóa đơn đầu vào và chứng từ thanh toán đầy đủ nhưng không thực hiện đầy đủ đăng ký thành lập địa điểm kinh doanh, không nộp thuế môn bài thì chi phí thuê kho sẽ bị loại khi tính (quyết toán) thuế thu nhập doanh nghiệp (TNDN).</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>heading</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>answers</t>
+  </si>
+  <si>
+    <t>reasoning types</t>
+  </si>
+  <si>
+    <t>goal</t>
+  </si>
+  <si>
+    <t>required_facts</t>
+  </si>
+  <si>
+    <t>supporting_rule_ids</t>
   </si>
 </sst>
 </file>
@@ -1521,27 +1536,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1549,6 +1555,30 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1830,1170 +1860,1944 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="53.88671875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="59" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="24.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="4" customWidth="1"/>
+    <col min="6" max="10" width="8.88671875" style="4"/>
+    <col min="11" max="11" width="77.6640625" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" ht="24" x14ac:dyDescent="0.2">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="N1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="17"/>
+    </row>
+    <row r="4" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="156" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="K4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5" t="s">
+      <c r="L4" s="2"/>
+      <c r="M4" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="216" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="17"/>
+    </row>
+    <row r="5" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="5" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="204" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="17"/>
+    </row>
+    <row r="6" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="K6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="84" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="17"/>
+    </row>
+    <row r="7" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="K7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="5" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="324" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="17"/>
+    </row>
+    <row r="8" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="252" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="17"/>
+    </row>
+    <row r="9" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="L9" s="2"/>
+      <c r="M9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="17"/>
+    </row>
+    <row r="10" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="L10" s="2"/>
+      <c r="M10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="17"/>
+    </row>
+    <row r="11" spans="1:19" ht="372" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="180" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="K11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="120" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="17"/>
+    </row>
+    <row r="12" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="J12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="K12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="17"/>
+    </row>
+    <row r="13" spans="1:19" ht="348" x14ac:dyDescent="0.2">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="L13" s="2"/>
+      <c r="M13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="120" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="17"/>
+    </row>
+    <row r="14" spans="1:19" ht="384" x14ac:dyDescent="0.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="17"/>
+    </row>
+    <row r="15" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="K15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="5" t="s">
+      <c r="L15" s="2"/>
+      <c r="M15" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="120" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="17"/>
+    </row>
+    <row r="16" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="J16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="L16" s="2"/>
+      <c r="M16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="156" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="17"/>
+    </row>
+    <row r="17" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="L17" s="2"/>
+      <c r="M17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="5" t="s">
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="17"/>
+    </row>
+    <row r="18" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="K18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="L18" s="2"/>
+      <c r="M18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="17"/>
+    </row>
+    <row r="19" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="J19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="K19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="5" t="s">
+      <c r="L19" s="2"/>
+      <c r="M19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="17"/>
+    </row>
+    <row r="20" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="72" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="K20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="L20" s="2"/>
+      <c r="M20" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="17"/>
+    </row>
+    <row r="21" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="J21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="K21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="9" t="s">
+      <c r="L21" s="2"/>
+      <c r="M21" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="192" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="17"/>
+    </row>
+    <row r="22" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="J22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="K22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="5" t="s">
+      <c r="L22" s="2"/>
+      <c r="M22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="17"/>
+    </row>
+    <row r="23" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="240" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="K23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="L23" s="2"/>
+      <c r="M23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="120" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="17"/>
+    </row>
+    <row r="24" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="J24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="K24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="5" t="s">
+      <c r="L24" s="2"/>
+      <c r="M24" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="132" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="17"/>
+    </row>
+    <row r="25" spans="1:19" ht="264" x14ac:dyDescent="0.2">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="J25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="K25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="5" t="s">
+      <c r="L25" s="2"/>
+      <c r="M25" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="84" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" ht="396" x14ac:dyDescent="0.2">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="J26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="K26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="5" t="s">
+      <c r="L26" s="2"/>
+      <c r="M26" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="120" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="17"/>
+    </row>
+    <row r="27" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="J27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="K27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="5" t="s">
+      <c r="L27" s="2"/>
+      <c r="M27" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="84" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="17"/>
+    </row>
+    <row r="28" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="J28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="K28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="9" t="s">
+      <c r="L28" s="2"/>
+      <c r="M28" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="17"/>
+    </row>
+    <row r="29" spans="1:19" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="J29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="K29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="5" t="s">
+      <c r="L29" s="2"/>
+      <c r="M29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="17"/>
+    </row>
+    <row r="30" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="48" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="K30" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="L30" s="2"/>
+      <c r="M30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="17"/>
+    </row>
+    <row r="31" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="17"/>
+    </row>
+    <row r="32" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="J32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="72" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="17"/>
+    </row>
+    <row r="33" spans="1:19" ht="408" x14ac:dyDescent="0.2">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="J33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="K33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="5" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="17"/>
+    </row>
+    <row r="34" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="J34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="K34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="9" t="s">
+      <c r="L34" s="2"/>
+      <c r="M34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="17"/>
+    </row>
+    <row r="35" spans="1:19" ht="408" x14ac:dyDescent="0.2">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="K35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="L35" s="2"/>
+      <c r="M35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="72" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="17"/>
+    </row>
+    <row r="36" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="J36" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="K36" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="5" t="s">
+      <c r="L36" s="2"/>
+      <c r="M36" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="17"/>
+    </row>
+    <row r="37" spans="1:19" ht="360" x14ac:dyDescent="0.2">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="J37" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="K37" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="5" t="s">
+      <c r="L37" s="2"/>
+      <c r="M37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="17"/>
+    </row>
+    <row r="38" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="K38" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="L38" s="2"/>
+      <c r="M38" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="204" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="17"/>
+    </row>
+    <row r="39" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="J39" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="K39" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="5" t="s">
+      <c r="L39" s="2"/>
+      <c r="M39" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="17"/>
+    </row>
+    <row r="40" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="K40" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="5" t="s">
+      <c r="L40" s="2"/>
+      <c r="M40" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="17"/>
+    </row>
+    <row r="41" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="K41" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="5" t="s">
+      <c r="L41" s="2"/>
+      <c r="M41" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="84" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="17"/>
+    </row>
+    <row r="42" spans="1:19" ht="384" x14ac:dyDescent="0.2">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="J42" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="K42" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="5" t="s">
+      <c r="L42" s="2"/>
+      <c r="M42" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="17"/>
+    </row>
+    <row r="43" spans="1:19" ht="336" x14ac:dyDescent="0.2">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="J43" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="K43" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="5" t="s">
+      <c r="L43" s="2"/>
+      <c r="M43" s="6" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="17"/>
+    </row>
+    <row r="44" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="J44" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="K44" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="9" t="s">
+      <c r="L44" s="2"/>
+      <c r="M44" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="17"/>
+    </row>
+    <row r="45" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="J45" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="K45" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="5" t="s">
+      <c r="L45" s="2"/>
+      <c r="M45" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="132" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="17"/>
+    </row>
+    <row r="46" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="J46" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="K46" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="5" t="s">
+      <c r="L46" s="2"/>
+      <c r="M46" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="168" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="17"/>
+    </row>
+    <row r="47" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="J47" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="K47" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="8" t="s">
+      <c r="L47" s="2"/>
+      <c r="M47" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="17"/>
+    </row>
+    <row r="48" spans="1:19" ht="360" x14ac:dyDescent="0.2">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C47" s="4" t="s">
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="17"/>
+    </row>
+    <row r="49" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="4" t="s">
+      <c r="K49" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="108" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="17"/>
+    </row>
+    <row r="50" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="J50" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="5" t="s">
+      <c r="K50" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="180" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="1"/>
-    </row>
-    <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="1"/>
-    </row>
-    <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="1"/>
-    </row>
-    <row r="61" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="1"/>
-    </row>
-    <row r="62" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="1"/>
-    </row>
-    <row r="64" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="1"/>
-    </row>
-    <row r="70" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="1"/>
-    </row>
-    <row r="71" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="1"/>
-    </row>
-    <row r="72" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="1"/>
-    </row>
-    <row r="73" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="1"/>
-    </row>
-    <row r="74" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="1"/>
-    </row>
-    <row r="75" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="1"/>
-    </row>
-    <row r="76" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="1"/>
-    </row>
-    <row r="77" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="1"/>
-    </row>
-    <row r="78" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="1"/>
-    </row>
-    <row r="79" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="1"/>
-    </row>
-    <row r="80" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="1"/>
-    </row>
-    <row r="81" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="1"/>
-    </row>
-    <row r="82" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="1"/>
-    </row>
-    <row r="83" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="1"/>
-    </row>
-    <row r="84" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="1"/>
-    </row>
-    <row r="85" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="1"/>
-    </row>
-    <row r="86" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="1"/>
-    </row>
-    <row r="87" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="1"/>
-    </row>
-    <row r="88" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="1"/>
-    </row>
-    <row r="89" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="1"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="1"/>
-    </row>
-    <row r="91" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="1"/>
-    </row>
-    <row r="92" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="1"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="1"/>
-    </row>
-    <row r="94" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="1"/>
-    </row>
-    <row r="95" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="1"/>
-    </row>
-    <row r="96" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="1"/>
-    </row>
-    <row r="97" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="1"/>
-    </row>
-    <row r="98" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="1"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="17"/>
+    </row>
+    <row r="51" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="9"/>
+    </row>
+    <row r="52" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="9"/>
+    </row>
+    <row r="53" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="9"/>
+    </row>
+    <row r="54" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="9"/>
+    </row>
+    <row r="55" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="9"/>
+    </row>
+    <row r="56" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="9"/>
+    </row>
+    <row r="57" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="9"/>
+    </row>
+    <row r="59" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="9"/>
+    </row>
+    <row r="60" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="9"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="9"/>
+    </row>
+    <row r="63" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="9"/>
+    </row>
+    <row r="64" spans="1:19" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="9"/>
+    </row>
+    <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="9"/>
+    </row>
+    <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="9"/>
+    </row>
+    <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="9"/>
+    </row>
+    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="9"/>
+    </row>
+    <row r="69" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="9"/>
+    </row>
+    <row r="70" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="9"/>
+    </row>
+    <row r="71" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="9"/>
+    </row>
+    <row r="72" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="9"/>
+    </row>
+    <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A73" s="15"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A74" s="15"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A75" s="15"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="9"/>
+    </row>
+    <row r="82" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="9"/>
+    </row>
+    <row r="83" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="9"/>
+    </row>
+    <row r="84" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="9"/>
+    </row>
+    <row r="85" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="9"/>
+    </row>
+    <row r="86" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="9"/>
+    </row>
+    <row r="87" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="9"/>
+    </row>
+    <row r="88" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="9"/>
+    </row>
+    <row r="89" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="9"/>
+    </row>
+    <row r="90" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="9"/>
+    </row>
+    <row r="91" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="9"/>
+    </row>
+    <row r="92" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="9"/>
+    </row>
+    <row r="93" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="9"/>
+    </row>
+    <row r="94" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="9"/>
+    </row>
+    <row r="95" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="9"/>
+    </row>
+    <row r="96" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="9"/>
+    </row>
+    <row r="97" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="9"/>
+    </row>
+    <row r="98" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="9"/>
+    </row>
+    <row r="99" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="9"/>
+    </row>
+    <row r="100" spans="1:6" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A100" s="15"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="9"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{1860D8C8-2383-4AD4-BB49-5CD2EAF54A82}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{41731F17-A284-4A54-920C-E906529F1E15}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{10D2A98D-2948-47D0-A2B6-61484379B7E2}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{957BABED-D27A-44E7-A368-E65AA36E037D}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{4FCFA616-828B-4DDD-BF91-8E7C533820D3}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{D113AF4D-CCB4-4059-A4BE-CCA4011CFBAF}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{1D69FF0C-0920-4CD1-A1BF-1947C9BDB2A0}"/>
-    <hyperlink ref="E9" r:id="rId8" display="https://luatvietnam.vn/luat-su-tu-van/doanh-nghiep-co-duoc-phep-quyen-gop-tu-thien-truoc-khi-pha-san-khong-145226-faqs.html" xr:uid="{69BEA38E-F6C1-4530-93EE-978BE2D96F49}"/>
-    <hyperlink ref="E10" r:id="rId9" display="https://luatvietnam.vn/luat-su-tu-van/doanh-nghiep-co-the-doi-lai-cac-khoan-no-sau-khi-chu-no-da-giai-the-khong-145672-faqs.html" xr:uid="{E08F0D75-B6B9-4329-B48D-BCE073EE7B19}"/>
-    <hyperlink ref="E11" r:id="rId10" display="https://luatvietnam.vn/luat-su-tu-van/co-can-ky-lai-hop-dong-lao-dong-khi-thay-doi-loai-hinh-doanh-nghiep-142929-faqs.html" xr:uid="{7EDDD11B-12D3-414E-A0CA-C08E1606D333}"/>
-    <hyperlink ref="E12" r:id="rId11" display="https://luatvietnam.vn/luat-su-tu-van/dieu-kien-tro-thanh-thanh-vien-hop-danh-cua-cong-ty-hop-danh-142639-faqs.html" xr:uid="{56DF7443-6B39-4761-B1AA-90E3329F31CB}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{C96D192F-E82C-45B3-B599-EBDEE1820C8A}"/>
-    <hyperlink ref="E15" r:id="rId13" xr:uid="{C7E260FD-2ED9-47F7-93FF-2E75D71696AC}"/>
-    <hyperlink ref="E14" r:id="rId14" display="https://luatvietnam.vn/luat-su-tu-van/mot-nguoi-duoc-thanh-lap-may-ho-kinh-doanh-132928-faqs.html" xr:uid="{FDBFC352-EBAA-4240-8DF2-F16A116E861E}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{EFDE32E7-DEC2-40A4-B42C-A20F66B2579B}"/>
-    <hyperlink ref="E17" r:id="rId16" display="https://luatvietnam.vn/luat-su-tu-van/y-nghia-cua-viec-nam-giu-51-ty-le-von-gop-132392-faqs.html" xr:uid="{B531F88A-EA9D-426D-B9F4-F1C96C10C1EB}"/>
-    <hyperlink ref="E18" r:id="rId17" xr:uid="{4AF7440C-2180-46FF-BCCD-1B7BF6D9E33B}"/>
-    <hyperlink ref="E19" r:id="rId18" display="https://luatvietnam.vn/luat-su-tu-van/nguoi-dai-dien-theo-phap-luat-cua-doanh-nghiep-tu-nhan-la-ai-132058-faqs.html" xr:uid="{A7F2DC10-796C-4216-9D0B-CEB4BBD63B43}"/>
-    <hyperlink ref="E20" r:id="rId19" display="https://luatvietnam.vn/luat-su-tu-van/loai-hinh-doanh-nghiep-phu-hop-cho-chuoi-cua-hang-132113-faqs.html" xr:uid="{66611880-BF8A-48BF-901B-2D7851F84302}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{9562C5E5-5132-4DF1-8FCE-1317AD057B66}"/>
-    <hyperlink ref="E22" r:id="rId21" display="https://luatvietnam.vn/luat-su-tu-van/gop-von-dieu-le-sai-hinh-thuc-bi-xu-phat-nhu-the-nao-131939-faqs.html" xr:uid="{F3A8CDB7-2103-45E2-8D2D-1560A90582BA}"/>
-    <hyperlink ref="E23" r:id="rId22" xr:uid="{25D8FABF-8286-41A4-8F49-F08358B9F54C}"/>
-    <hyperlink ref="E24" r:id="rId23" xr:uid="{A877935F-CDB2-417A-8584-74EAC652C71E}"/>
-    <hyperlink ref="E25" r:id="rId24" xr:uid="{E9391B07-1A47-4C07-A72C-01985BC906ED}"/>
-    <hyperlink ref="E26" r:id="rId25" xr:uid="{86742649-F876-4CA1-9EB8-015EB2C6B2DF}"/>
-    <hyperlink ref="E27" r:id="rId26" xr:uid="{2E52EA87-8C4E-4D95-B8A6-7D70B036AD1A}"/>
-    <hyperlink ref="E28" r:id="rId27" xr:uid="{AA341052-5015-4699-9137-BB6810475DBB}"/>
-    <hyperlink ref="E29" r:id="rId28" display="https://luatvietnam.vn/luat-su-tu-van/ho-so-thanh-lap-chi-nhanh-cong-ty-129269-faqs.html" xr:uid="{44162626-128B-435B-A15D-365F31AD8D42}"/>
-    <hyperlink ref="E30" r:id="rId29" xr:uid="{ED586243-FA70-499D-B297-3B2C3FA790FB}"/>
-    <hyperlink ref="E31" r:id="rId30" xr:uid="{9341866A-6B21-4245-8537-316628F2C92A}"/>
-    <hyperlink ref="E32" r:id="rId31" xr:uid="{81DA7E1B-0BD7-4854-8BD6-6B2345BF2903}"/>
-    <hyperlink ref="E33" r:id="rId32" display="https://luatvietnam.vn/luat-su-tu-van/lap-dia-diem-kinh-doanh-khac-tinh-dat-tru-so-chinh-128749-faqs.html" xr:uid="{696495E2-D741-4445-9E2D-7871F0313242}"/>
-    <hyperlink ref="E34" r:id="rId33" display="https://luatvietnam.vn/luat-su-tu-van/cong-ty-con-co-duoc-mua-co-phan-cua-cong-ty-me-128764-faqs.html" xr:uid="{8F3C09FA-60EF-4D61-A3A9-8BAEDC0AAB00}"/>
-    <hyperlink ref="E35" r:id="rId34" xr:uid="{3B7FADDD-AA19-492B-9B03-B64F154F6212}"/>
-    <hyperlink ref="E36" r:id="rId35" xr:uid="{849F54EC-E025-4FF4-B66F-5E9C38F9B1CF}"/>
-    <hyperlink ref="E37" r:id="rId36" display="https://luatvietnam.vn/luat-su-tu-van/ban-hang-tap-hoa-co-can-dong-thue-khong--149064-faqs.html" xr:uid="{EEDFE3AF-5D33-4111-B2DD-D2C8C71CEB1E}"/>
-    <hyperlink ref="E38" r:id="rId37" xr:uid="{D4D386E8-6263-45BB-A191-6C1170740E4C}"/>
-    <hyperlink ref="E39" r:id="rId38" xr:uid="{05BDCFCE-914B-41A8-A35B-B8D4EED37CFA}"/>
-    <hyperlink ref="E40" r:id="rId39" xr:uid="{A4C6670D-7CA6-42B5-83B5-ABAFC94508AF}"/>
-    <hyperlink ref="E41" r:id="rId40" xr:uid="{7C2F3CB8-29B4-4B0C-B411-2C4533F77F7A}"/>
-    <hyperlink ref="E42" r:id="rId41" xr:uid="{F2FF1BE1-BDC3-469C-BFAA-2162987D3C3E}"/>
-    <hyperlink ref="E43" r:id="rId42" display="https://luatvietnam.vn/luat-su-tu-van/chi-nhanh-co-phai-dang-ki-noi-quy-lao-dong-khong-144160-faqs.html" xr:uid="{04702A48-FEAA-4523-8810-41C90063E4E9}"/>
-    <hyperlink ref="E44" r:id="rId43" xr:uid="{77022659-16B9-4FDF-8030-929271D03EC9}"/>
-    <hyperlink ref="E45" r:id="rId44" xr:uid="{8D18D450-0F0C-42C0-9821-9D3340693236}"/>
-    <hyperlink ref="E46" r:id="rId45" display="https://luatvietnam.vn/luat-su-tu-van/thanh-vien-cong-ty-rut-von-bo-tron-phai-lam-the-nao-142135-faqs.html" xr:uid="{F989C5E9-7E36-4A56-BA5E-F08B47ED7C13}"/>
-    <hyperlink ref="E47" r:id="rId46" xr:uid="{D72224EC-40A0-44B1-A32C-11301901D184}"/>
-    <hyperlink ref="E48" r:id="rId47" xr:uid="{48DFB3E9-02A4-49DA-8270-26564B9E6D05}"/>
-    <hyperlink ref="E49" r:id="rId48" xr:uid="{034A17E0-182E-456C-8C83-F50578E341B5}"/>
-    <hyperlink ref="E50" r:id="rId49" display="https://luatvietnam.vn/luat-su-tu-van/thue-kho-chua-hang-co-phai-dang-ky-kinh-doanh-khong-137398-faqs.html" xr:uid="{F05C1461-FCC0-4772-A46E-0A2414967765}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{6C6AEE77-1523-4C3C-8D50-7F24C13E7C7C}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{52AFD201-03FA-4D08-BBC0-01909F5FEB12}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{678A1BC0-BB4F-4A53-8E73-50E0BDE82A05}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{ED039E05-EBC0-45F9-BA01-F07A3852A732}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{CDEE7759-8156-43A4-9591-7DF99E94B4F1}"/>
+    <hyperlink ref="M7" r:id="rId6" xr:uid="{FC4EEB4C-1E58-45ED-99D9-363B667D9172}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{D9117279-20AB-4054-A3CE-259BA814A459}"/>
+    <hyperlink ref="M9" r:id="rId8" display="https://luatvietnam.vn/luat-su-tu-van/doanh-nghiep-co-duoc-phep-quyen-gop-tu-thien-truoc-khi-pha-san-khong-145226-faqs.html" xr:uid="{92DF261E-B530-48EF-9E96-E2E972FD1AAF}"/>
+    <hyperlink ref="M10" r:id="rId9" display="https://luatvietnam.vn/luat-su-tu-van/doanh-nghiep-co-the-doi-lai-cac-khoan-no-sau-khi-chu-no-da-giai-the-khong-145672-faqs.html" xr:uid="{22B5EAB6-070D-4A5F-A526-D2587DFDCA73}"/>
+    <hyperlink ref="M11" r:id="rId10" display="https://luatvietnam.vn/luat-su-tu-van/co-can-ky-lai-hop-dong-lao-dong-khi-thay-doi-loai-hinh-doanh-nghiep-142929-faqs.html" xr:uid="{DADAD542-FDA9-4D49-8F55-84B12D0A79EC}"/>
+    <hyperlink ref="M12" r:id="rId11" display="https://luatvietnam.vn/luat-su-tu-van/dieu-kien-tro-thanh-thanh-vien-hop-danh-cua-cong-ty-hop-danh-142639-faqs.html" xr:uid="{723B1D2B-31DE-451D-AF41-92921D898BF4}"/>
+    <hyperlink ref="M13" r:id="rId12" xr:uid="{C174ECEE-13E8-428D-AF4E-2D1A5C36ACC8}"/>
+    <hyperlink ref="M15" r:id="rId13" xr:uid="{AAD8BD70-59C9-458F-915B-FF7352A55537}"/>
+    <hyperlink ref="M14" r:id="rId14" display="https://luatvietnam.vn/luat-su-tu-van/mot-nguoi-duoc-thanh-lap-may-ho-kinh-doanh-132928-faqs.html" xr:uid="{FED2E370-E4DD-480B-AECE-A85012EC5F02}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{77F8ED63-F739-4A8E-A621-8001C63D632B}"/>
+    <hyperlink ref="M17" r:id="rId16" display="https://luatvietnam.vn/luat-su-tu-van/y-nghia-cua-viec-nam-giu-51-ty-le-von-gop-132392-faqs.html" xr:uid="{60BF101E-9FDA-400B-AC29-CDDD6EE339E6}"/>
+    <hyperlink ref="M18" r:id="rId17" xr:uid="{533D9651-1FDF-475B-B3F1-C83EED351E37}"/>
+    <hyperlink ref="M19" r:id="rId18" display="https://luatvietnam.vn/luat-su-tu-van/nguoi-dai-dien-theo-phap-luat-cua-doanh-nghiep-tu-nhan-la-ai-132058-faqs.html" xr:uid="{876535F6-1BD1-4D3D-8668-473FA0B053DD}"/>
+    <hyperlink ref="M20" r:id="rId19" display="https://luatvietnam.vn/luat-su-tu-van/loai-hinh-doanh-nghiep-phu-hop-cho-chuoi-cua-hang-132113-faqs.html" xr:uid="{C4CBE498-22F7-4355-BA58-D7CE5C5D3DE3}"/>
+    <hyperlink ref="M21" r:id="rId20" xr:uid="{76C659A6-A586-4517-A79E-95E09352CF66}"/>
+    <hyperlink ref="M22" r:id="rId21" display="https://luatvietnam.vn/luat-su-tu-van/gop-von-dieu-le-sai-hinh-thuc-bi-xu-phat-nhu-the-nao-131939-faqs.html" xr:uid="{219B5EF7-6E46-446E-AFDC-87A35C00D7EA}"/>
+    <hyperlink ref="M23" r:id="rId22" xr:uid="{5F5E7216-8E78-49F4-B5D7-05A01B0B2457}"/>
+    <hyperlink ref="M24" r:id="rId23" xr:uid="{1D29D7FE-69E2-4264-8753-D887D8028FE6}"/>
+    <hyperlink ref="M25" r:id="rId24" xr:uid="{DA5E4669-4697-4336-96E9-791DE8C2CB5C}"/>
+    <hyperlink ref="M26" r:id="rId25" xr:uid="{43FC8731-F378-4636-A93E-AAA7DA30D9B6}"/>
+    <hyperlink ref="M27" r:id="rId26" xr:uid="{9241AB60-57F6-4889-9825-C288D39DE0E8}"/>
+    <hyperlink ref="M28" r:id="rId27" xr:uid="{CC55DEAE-E4BA-4513-AF02-381DDE669DF7}"/>
+    <hyperlink ref="M29" r:id="rId28" display="https://luatvietnam.vn/luat-su-tu-van/ho-so-thanh-lap-chi-nhanh-cong-ty-129269-faqs.html" xr:uid="{2CB24872-88E2-4AF0-B566-01E811458AB2}"/>
+    <hyperlink ref="M30" r:id="rId29" xr:uid="{67C7683F-680B-49FF-B0B8-86EAC4273C4E}"/>
+    <hyperlink ref="M31" r:id="rId30" xr:uid="{04C7C697-BB8F-4A5C-9D22-859BE3AF716B}"/>
+    <hyperlink ref="M32" r:id="rId31" xr:uid="{7C8520F6-168B-41FB-A206-7024EC27E414}"/>
+    <hyperlink ref="M33" r:id="rId32" display="https://luatvietnam.vn/luat-su-tu-van/lap-dia-diem-kinh-doanh-khac-tinh-dat-tru-so-chinh-128749-faqs.html" xr:uid="{0919A7BA-4956-4D4B-BBF0-0AAA01E29CDF}"/>
+    <hyperlink ref="M34" r:id="rId33" display="https://luatvietnam.vn/luat-su-tu-van/cong-ty-con-co-duoc-mua-co-phan-cua-cong-ty-me-128764-faqs.html" xr:uid="{B0154FCC-23B3-4C9E-99E2-EAAC830FE8B6}"/>
+    <hyperlink ref="M35" r:id="rId34" xr:uid="{2F22A66F-C8AA-4EB3-8B10-7E3F20FCC07E}"/>
+    <hyperlink ref="M36" r:id="rId35" xr:uid="{DE1328A4-C98A-4642-9A0F-5528A319316C}"/>
+    <hyperlink ref="M37" r:id="rId36" display="https://luatvietnam.vn/luat-su-tu-van/ban-hang-tap-hoa-co-can-dong-thue-khong--149064-faqs.html" xr:uid="{2589003E-F216-467A-8D68-F7CF9D9F02DD}"/>
+    <hyperlink ref="M38" r:id="rId37" xr:uid="{015C9998-F756-449A-9CB7-46A211107313}"/>
+    <hyperlink ref="M39" r:id="rId38" xr:uid="{73C94DA4-CA59-45A3-B85B-2BFF3842A13B}"/>
+    <hyperlink ref="M40" r:id="rId39" xr:uid="{A7DB327F-0ECF-4678-AA23-BD385CE38D36}"/>
+    <hyperlink ref="M41" r:id="rId40" xr:uid="{3ACE7517-4E89-40F2-947E-15C596D7A87C}"/>
+    <hyperlink ref="M42" r:id="rId41" xr:uid="{5EF00FC4-D7EB-4BC5-B823-BEDC051A50D3}"/>
+    <hyperlink ref="M43" r:id="rId42" display="https://luatvietnam.vn/luat-su-tu-van/chi-nhanh-co-phai-dang-ki-noi-quy-lao-dong-khong-144160-faqs.html" xr:uid="{A0AE31BA-667E-4D25-A01D-EFB7702355EF}"/>
+    <hyperlink ref="M44" r:id="rId43" xr:uid="{D335A192-9CF4-495A-96DF-D3BCCA59DE11}"/>
+    <hyperlink ref="M45" r:id="rId44" xr:uid="{33522961-F6B7-4DB7-BFAA-4586BDB9642F}"/>
+    <hyperlink ref="M46" r:id="rId45" display="https://luatvietnam.vn/luat-su-tu-van/thanh-vien-cong-ty-rut-von-bo-tron-phai-lam-the-nao-142135-faqs.html" xr:uid="{9925C92B-7139-467F-B2E7-3C0CB60D24ED}"/>
+    <hyperlink ref="M47" r:id="rId46" xr:uid="{E0B14359-E4B1-4C8E-8DD7-6E5AA5E8B22A}"/>
+    <hyperlink ref="M48" r:id="rId47" xr:uid="{023372B2-EF7F-4B24-916B-14689F46B2A1}"/>
+    <hyperlink ref="M49" r:id="rId48" xr:uid="{39BFC607-7FB5-4454-A26A-E1787382E055}"/>
+    <hyperlink ref="M50" r:id="rId49" display="https://luatvietnam.vn/luat-su-tu-van/thue-kho-chua-hang-co-phai-dang-ky-kinh-doanh-khong-137398-faqs.html" xr:uid="{606F9310-59E9-4FE0-9868-61FB8298E54B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
